--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zen/teaching/ASTR302_2026B/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2210A3C1-1738-7542-9764-D4C8C81511D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C438C351-8F7D-284F-A706-5798F6FB7CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11000" yWindow="500" windowWidth="23100" windowHeight="17560" xr2:uid="{852DEBEA-2124-C54D-8007-05A8DCAE437B}"/>
   </bookViews>
@@ -463,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -477,14 +477,12 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -799,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F24B1B89-A7AD-9F46-8F0C-36254C220784}">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -830,7 +828,7 @@
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="14">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -841,7 +839,7 @@
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="14">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -852,10 +850,10 @@
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="14">
         <v>1</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>56</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -866,7 +864,7 @@
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="15">
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -877,7 +875,7 @@
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="15">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -888,10 +886,10 @@
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="15">
         <v>2</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>64</v>
       </c>
     </row>
@@ -935,7 +933,7 @@
       <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="16">
         <v>4</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -946,7 +944,7 @@
       <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="16">
         <v>4</v>
       </c>
       <c r="C12" s="6" t="s">
@@ -957,10 +955,10 @@
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="16">
         <v>4</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="16" t="s">
         <v>65</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -971,7 +969,7 @@
       <c r="A14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="17">
         <v>5</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -982,7 +980,7 @@
       <c r="A15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="17">
         <v>5</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -993,10 +991,10 @@
       <c r="A16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="17">
         <v>5</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="17" t="s">
         <v>72</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -1007,7 +1005,7 @@
       <c r="A17" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="13">
         <v>6</v>
       </c>
       <c r="C17" s="8" t="s">
@@ -1018,7 +1016,7 @@
       <c r="A18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="13">
         <v>6</v>
       </c>
       <c r="C18" s="8" t="s">
@@ -1029,10 +1027,10 @@
       <c r="A19" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="13">
         <v>6</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="13" t="s">
         <v>72</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -1046,7 +1044,7 @@
       <c r="A20" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="18">
         <v>7</v>
       </c>
       <c r="C20" s="9" t="s">
@@ -1057,7 +1055,7 @@
       <c r="A21" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="18">
         <v>7</v>
       </c>
       <c r="C21" s="9" t="s">
@@ -1068,10 +1066,10 @@
       <c r="A22" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="18">
         <v>7</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>104</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -1082,7 +1080,7 @@
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="15">
         <v>8</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -1093,7 +1091,7 @@
       <c r="A24" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="15">
         <v>8</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -1104,16 +1102,16 @@
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="15">
         <v>8</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="15" t="s">
         <v>74</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="1" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1157,7 +1155,7 @@
       <c r="A29" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="16">
         <v>10</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -1168,7 +1166,7 @@
       <c r="A30" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="16">
         <v>10</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -1179,10 +1177,10 @@
       <c r="A31" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="16">
         <v>10</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="16" t="s">
         <v>101</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -1196,7 +1194,7 @@
       <c r="A32" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="17">
         <v>11</v>
       </c>
       <c r="C32" s="7" t="s">
@@ -1207,7 +1205,7 @@
       <c r="A33" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="17">
         <v>11</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -1221,10 +1219,10 @@
       <c r="A34" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="17">
         <v>11</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="17" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1232,7 +1230,7 @@
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="15">
         <v>12</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -1254,7 +1252,7 @@
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="15">
         <v>12</v>
       </c>
       <c r="C37" s="4"/>
@@ -1301,7 +1299,7 @@
       <c r="A41" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="16">
         <v>14</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -1312,10 +1310,10 @@
       <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="16">
         <v>14</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="16" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1334,7 +1332,7 @@
       <c r="A44" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="17">
         <v>15</v>
       </c>
       <c r="C44" s="7" t="s">
@@ -1348,10 +1346,10 @@
       <c r="A45" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="18">
+      <c r="B45" s="17">
         <v>15</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1359,10 +1357,10 @@
       <c r="A46" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="18">
+      <c r="B46" s="17">
         <v>15</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1370,7 +1368,7 @@
       <c r="A47" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="14">
+      <c r="B47" s="13">
         <v>16</v>
       </c>
       <c r="C47" s="8" t="s">
@@ -1381,7 +1379,7 @@
       <c r="A48" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="14">
+      <c r="B48" s="13">
         <v>16</v>
       </c>
       <c r="C48" s="8" t="s">
@@ -1392,30 +1390,15 @@
       <c r="A49" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="14">
+      <c r="B49" s="13">
         <v>16</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="C49" s="13" t="s">
         <v>52</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="13"/>
-      <c r="B50" s="20"/>
-      <c r="C50" s="13"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="13"/>
-      <c r="B51" s="20"/>
-      <c r="C51" s="13"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="13"/>
-      <c r="B52" s="20"/>
-      <c r="C52" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
